--- a/11-CollaborationList/Strathclyde.xlsx
+++ b/11-CollaborationList/Strathclyde.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethlong/Library/CloudStorage/Box-Box/CubMac-Box/KL-GIT/CCAP/02-LhARA/00-Collaboration-lists/11-CollaborationList/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2050112171436/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2782C61A-DEB8-0449-81FE-6649158CB3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:9_{2782C61A-DEB8-0449-81FE-6649158CB3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C3B0A7-C7B4-B34A-9AC3-E8880BEF4946}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12120" windowWidth="57600" windowHeight="16220" xr2:uid="{BC688C27-9C2C-C845-8744-FF1C33AFE83C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{BC688C27-9C2C-C845-8744-FF1C33AFE83C}"/>
   </bookViews>
   <sheets>
     <sheet name="Strathclyde" sheetId="1" r:id="rId1"/>
@@ -148,9 +148,6 @@
     <t>Robert Bingham</t>
   </si>
   <si>
-    <t>CLF</t>
-  </si>
-  <si>
     <t>Central Laser Facility, STFC Rutherford Appleton Laboratory, Harwell Oxford, Didcot OX11 0QX, UK</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
   </si>
   <si>
     <t>M.Alderton</t>
+  </si>
+  <si>
+    <t>STFC-CLF</t>
   </si>
 </sst>
 </file>
@@ -1206,13 +1206,13 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" t="s">
         <v>20</v>
@@ -1221,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
@@ -1262,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
@@ -1288,7 +1288,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -1329,7 +1329,7 @@
         <v>41</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" t="s">
         <v>20</v>
@@ -1338,36 +1338,36 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>43</v>
-      </c>
-      <c r="N5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
       </c>
       <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H6" t="s">
         <v>20</v>
@@ -1376,39 +1376,39 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="N6" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" t="s">
         <v>50</v>
-      </c>
-      <c r="O6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
         <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
       </c>
       <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
         <v>20</v>
@@ -1419,25 +1419,25 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
         <v>59</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>60</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" t="s">
         <v>63</v>
       </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" t="s">
         <v>20</v>
@@ -1448,25 +1448,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>66</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
         <v>20</v>
